--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/loytel.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/loytel.xlsx
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">Why!</t>
   </si>
   <si>
-    <t xml:space="preserve">考えても見ろ。この竜は黄金を食べるんだろう？そんな竜を、貧乏な我々がどうやって養うというのだ？</t>
+    <t xml:space="preserve">考えてもみろ。この竜は黄金を食べるんだろう？そんな竜を、貧乏な我々がどうやって養うというのだ？</t>
   </si>
   <si>
     <t xml:space="preserve">Think about it. This dragon eats gold, doesn’t it? How are we supposed to feed it when we are hardly wealthy?</t>
@@ -5165,7 +5165,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
       <alignment/>
       <protection locked="1"/>
@@ -5288,10 +5288,6 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
       <protection locked="1"/>
     </xf>
   </cellXfs>
@@ -13827,7 +13823,7 @@
       <c r="I686" s="1">
         <v>411</v>
       </c>
-      <c r="J686" s="31" t="s">
+      <c r="J686" s="7" t="s">
         <v>784</v>
       </c>
       <c r="K686" s="4" t="s">
